--- a/apps/archetest/docs/question-review/question-review-hh.xlsx
+++ b/apps/archetest/docs/question-review/question-review-hh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$16</definedName>
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Поэтому у этого пакета есть срок: вердикты нужны к вс 02.08.</t>
+          <t>Срока нет (прежний дедлайн 02.08 снят вместе с фестивальным спринтом).</t>
         </is>
       </c>
     </row>

--- a/apps/archetest/docs/question-review/question-review-hh.xlsx
+++ b/apps/archetest/docs/question-review/question-review-hh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$16</definedName>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -479,312 +479,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ревью вопросов Архетеста — 15 вопросов новой шкалы «Доброжелательность» (HON)</t>
+          <t>Авторские вопросы Archetest — редакция v2, 2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проведено внутреннее содержательное ревью Codex; это не заключение комиссии психологов.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Этих вопросов ЕЩЁ НЕТ в тесте. В отличие от пакетов 5.1 и 5.5, где вопросы уже</t>
+          <t>Отчёт: prepared-batches-review-2026-10-16.md и JSON с исходниками, ключами и замечаниями.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>работают и ревью их улучшает, здесь ваши вердикты решают, что попадёт в тест.</t>
+          <t>Пакеты включены в рабочий банк для пилота. Интервью и эмпирическая валидация не проведены.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Срока нет (прежний дедлайн 02.08 снят вместе с фестивальным спринтом).</t>
+          <t>Период: последние шесть месяцев; варианты: никогда / редко / часто / почти каждый раз.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Нет подходящих ситуаций или трудно ответить — пропуск, а не нулевой балл.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Зачем шкала:</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>СДВГ: обычные условия с привычной поддержкой; 9 областей INA и 9 HYI; это не ASRS.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Прототип конструкта — Honesty-Humility из модели HEXACO (Ashton &amp; Lee, 2009).</t>
+          <t>Привязанность: одни выбранные безопасные близкие отношения; без вывода о стиле.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Формулировки авторские: пункты HEXACO не заимствуются, только уровень конструкта.</t>
+          <t>HON: честность–скромность, четыре фасета; не Agreeableness и не тест нравственности.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Практическая цель — проверить на своих данных спор в литературе: отличим ли</t>
+          <t>HON имеет обратный ключ 3/2/1/0; остальные новые пункты — прямой 0/1/2/3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>«тёмный фактор» личности от обычного антагонизма/недоброжелательности. Сейчас</t>
+          <t>Стратегии помощи, вежливость, экономия и разумные границы сами по себе не дают баллов.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>проверить это невозможно — шкалы Доброжелательности в тесте нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Главный риск, ради которого мы и просим ревью:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Три из четырёх фасетов Доброжелательности — почти антонимы наших тёмных шкал</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>(Искренность ↔ макиавеллизм, Справедливость ↔ антисоциальность, Скромность ↔</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>нарциссизм). Если вопросы получились ЗЕРКАЛОМ тёмных — «то же самое наоборот», —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>то корреляция выйдет артефактом дизайна, и вся проверка обесценится.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Просьба смотреть каждый вопрос через этот фильтр: не является ли он просто</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>перевёрнутым вопросом про макиавеллизм/антисоциальность/нарциссизм?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Фасет «Нежадность» — якорный: он дальше всех от тёмных шкал (деньги, статус,</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>роскошь), и именно он даёт расхождению шанс проявиться. К нему особое внимание.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Четыре фасета (колонка «Шкала» показывает фасет каждого вопроса):</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>• Искренность — 4 вопроса: отсутствие притворства и удобной лжи, в т. ч. без выгоды.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>• Справедливость — 4: не пользоваться другими и правилами в свою пользу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ⚠️ Намеренно НЕ про нарушение закона — это была бы антисоциальность.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>• Нежадность — 4: деньги, статус и роскошь не в центре жизни (якорный фасет).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>• Скромность — 3: не претендую на особое отношение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ⚠️ Намеренно НЕ про самооценку — это была бы нарциссическая шкала.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Коротко по таблице:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>• Лист «Вопросы»: один вопрос = одна строка. Варианты А–Г — с баллами в скобках.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>• Варианты скорят ТОЛЬКО HON, ни одного балла другим шкалам — это методологическое</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  требование: общие пункты сделали бы корреляцию артефактом. Пустые скобки = дистрактор.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>• «Обр.» = да — reverse-вопрос: балл набирается вариантом, который выглядит невыгодно</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  или неловко (признать, что не смотрел; заплатить, хотя можно не платить; не пойти</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  «по знакомству» ради близкого). Проверьте, что инверсия психологически честная.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>• «Вердикт»: ОК / Править / Удалить. «Комментарий / правка» — формулировку можно</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  прямо в ячейке. Правки внесём мы, присылать файл целиком не нужно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Что важнее полировки:</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>1. Зеркальность (см. выше) — главный критерий.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>2. Социальная желательность. У этой шкалы она острее, чем у тёмных: «правильный»</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   вариант виден. Если вопрос читается как «выберите добродетель» — он бесполезен,</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   его выберут все. Скажите, где это так.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>3. Покрытие фасета: 3–4 вопроса на фасет — достаточно ли они разные по ситуациям?</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>4. Язык и этика — те же критерии, что для 5.1 (см. INSTRUCTIONS.md).</t>
+          <t>Следующий этап: реальные когнитивные интервью и проверка измерительных свойств.</t>
         </is>
       </c>
     </row>
@@ -886,38 +658,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Сосед третий раз за месяц просит подвезти его до работы — вам не по пути, крюк минут двадцать.</t>
+          <t>За последние шесть месяцев как часто обращаясь к человеку за услугой, вы изображаете больше личной симпатии, чем на самом деле чувствуете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Говорю прямо, что мне неудобно, и предлагаю скинуться на такси
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, но потом «случайно» выезжаю раньше, чтобы он не успел
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Ссылаюсь на несуществующие дела — так мягче
-[]</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Подвожу и молчу, хотя раздражаюсь
-[]</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -940,35 +724,43 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Вы опоздали на встречу, потому что проспали. Вас спрашивают, что случилось.</t>
+          <t>За последние шесть месяцев как часто рассказывая о своей ошибке, вы сознательно придумываете внешнюю причину, чтобы представить себя в более выгодном свете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Говорю как есть: проспал
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>«Пробки» — звучит уважительнее и никого не задевает
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Ссылаюсь на затянувшийся звонок: формально почти правда
-[]</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Извиняюсь, но причину не называю вовсе
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -991,35 +783,43 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>В компании увлечённо обсуждают сериал, которого вы не смотрели. К вам поворачиваются: «Ну а ты как считаешь?»</t>
+          <t>За последние шесть месяцев как часто ради расположения собеседника вы делаете вид, что разделяете его увлечение, хотя это не так? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Говорю, что не смотрел, и слушаю дальше
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Отвечаю общо — по обрывкам разговора вполне можно поддержать
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Пересказываю чужое мнение как своё, я его где-то слышал
-[]</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Перевожу тему на то, в чём разбираюсь
-[]</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1042,35 +842,43 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Вы заполняете анкету в приложении для знакомств. Поля про рост, доход, увлечения.</t>
+          <t>За последние шесть месяцев как часто представляя себя новым знакомым, вы приписываете себе достижения, которых у вас не было? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Пишу как есть, включая скучные места
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Округляю в свою пользу — так делают все
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Добавляю увлечения, которые были давно и недолго
-[]</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Оставляю неудобные поля пустыми
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1086,38 +894,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Продаёте свой велосипед. Вы знаете, что через сезон придётся менять узел — по виду это не заметно.</t>
+          <t>За последние шесть месяцев как часто при продаже своей вещи вы намеренно скрываете известный вам существенный недостаток, чтобы получить больше денег? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Говорю про узел сам и ставлю цену с учётом этого
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Скажу, если спросят прямо; сам тему не поднимаю
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [HON 1]</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Продаю как есть: осматривать — задача покупателя
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Перед продажей вычищаю и полирую, чтобы выглядел свежее
-[]</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1140,35 +960,43 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>В доме собирают деньги на замену домофона. Сбор добровольный, домофон поставят в любом случае.</t>
+          <t>За последние шесть месяцев как часто при посильном общем расходе вы уклоняетесь от заранее согласованной доли, рассчитывая, что остальные оплатят её за вас? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Сдаю свою долю — пользоваться буду наравне со всеми
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Не сдаю: раз добровольно, значит без меня обошлись
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Сдаю меньше, чем просят, — у меня и старый работал
-[]</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Сдаю, но хочу, чтобы это было видно в общем чате
-[]</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1184,38 +1012,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>У вас есть карта со скидкой, по правилам действующая только на ваши покупки. Знакомые просят покупать через вас.</t>
+          <t>За последние шесть месяцев как часто вы используете ошибку в расчёте в свою пользу, хотя знаете, что из-за неё другой человек получит меньше положенного? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Объясняю, что карта не для этого, и отказываюсь
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Изредка и только самым близким
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [HON 1]</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Покупаю всем: правило формальное, никто не пострадает
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Покупаю, но беру себе часть разницы за хлопоты
-[]</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1231,38 +1071,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Вы вдвоём с двоюродным братом разбираете гараж покойного дяди. В хламе вам попадается вещь, которая заметно дороже, чем кажется.</t>
+          <t>За последние шесть месяцев как часто деля общую находку, вы скрываете её известную вам ценность, чтобы получить большую долю? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Сразу говорю брату, оцениваем и решаем вместе
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Говорю, но напоминаю, что нашёл её всё-таки я
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [HON 1]</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Забираю себе: кто разбирал, тот и нашёл
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Предлагаю отдать тому, кому дядя был дороже
-[]</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1278,38 +1130,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Вам подняли зарплату на треть. Через полгода вы замечаете, что…</t>
+          <t>За последние шесть месяцев как часто при выборе вещи для вас решающим становится то, подчеркнёт ли она ваш достаток, а не удобство или качество? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>живу примерно как раньше, разница уходит в накопления
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>сразу подтянул уровень: машина, район, рестораны
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>стал чаще звать друзей за свой счёт
-[]</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>трачу больше, но не могу вспомнить на что
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1332,35 +1196,43 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Вы выбираете жильё. Один вариант — престижный район на пределе бюджета, другой — проще, но с запасом денег каждый месяц.</t>
+          <t>За последние шесть месяцев как часто вы хотите более престижную вещь именно ради того, чтобы окружающие считали вас обеспеченными? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Беру то, что проще: запас важнее адреса
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Беру престижный: такие вложения себя оправдывают
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Беру престижный — вокруг будут люди другого уровня
-[]</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Смотрю только на дорогу до работы, остальное неважно
-[]</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1376,38 +1248,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Планируете поездку. За те же дни можно жить в обычном месте или в дорогом, о котором потом будете рассказывать.</t>
+          <t>За последние шесть месяцев как часто вам трудно довольствоваться удобной покупкой, если более дорогая версия сильнее подчёркивала бы ваш статус? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Обычное: деньги лучше потратить на саму поездку
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Дорогое: раз в год можно себе позволить лучшее
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Дорогое: с него и фотографии другие
-[]</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Возьму обычное, но буду жалеть, что не дорогое
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1430,35 +1314,43 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Вам предлагают дело, где доход заметно выше нынешнего, но свободного времени почти не останется.</t>
+          <t>За последние шесть месяцев как часто сравнивая свои вещи с более дорогими вещами знакомых, вы чувствуете потребность показать, что можете позволить себе не меньше? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Отказываюсь: мне хватает того, что есть
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь: от таких денег не отказываются
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Соглашаюсь на пару лет, а потом посмотрю
-[]</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Торгуюсь, чтобы и доход был, и время осталось
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1481,35 +1373,43 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Вы много лет занимаетесь своим делом. Новый знакомый, не зная этого, с жаром объясняет вам его основы.</t>
+          <t>За последние шесть месяцев как часто в общении вы ожидаете особого обращения именно потому, что считаете себя выше окружающих? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Слушаю, не обозначая свой уровень
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Мягко даю понять, что в теме, — иначе неловко нам обоим
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [HON 1]</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Сразу говорю, сколько лет этим занимаюсь
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Задаю вопрос, после которого станет ясно, кто здесь кто
-[]</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1525,38 +1425,50 @@
           <t>HON</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Детскую площадку во дворе делали втроём. Соседи благодарят при всех вас одного.</t>
+          <t>За последние шесть месяцев как часто при общей благодарности вы намеренно умалчиваете о сопоставимом вкладе других, чтобы главная заслуга досталась вам? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Тут же называю остальных двоих
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Говорю «делали вместе», без имён
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [HON 1]</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Принимаю благодарность: я и правда вложился больше всех
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Отшучиваюсь и перевожу тему
-[]</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1579,41 +1491,49 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Близкому человеку предстоит отбор, где всё решает общий порядок. У вас есть знакомство, через которое «вопрос решается».</t>
+          <t>За последние шесть месяцев как часто в ситуации с одинаковыми для всех правилами вы считаете, что именно вам положено исключение из-за вашего особого положения? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Не пользуюсь: пусть проходит общим путём
+          <t>Никогда или почти никогда
 [HON 3]</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Позвоню — на его месте так поступил бы любой
+          <t>Редко
+[HON 2]</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HON 1]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 []</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Не прошу решить, но упомяну, что это мой человек
-[]</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Спрошу у него самого, хочет ли он так
-[HON 1]</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K16"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править или Удалить" type="list">
-      <formula1>"ОК,Править,Удалить"</formula1>
+    <dataValidation sqref="J2:J16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править, Удалить или Для пилота" type="list">
+      <formula1>"ОК,Править,Удалить,Для пилота"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
